--- a/Hoadon/HDRa/9/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/9/Hoadondientu.xlsx
@@ -314,6 +314,338 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-177</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM MẠNG LƯỚI MOBIFONE MIỀN NAM-CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>MM18 Trường Sơn, Phường Diên Hồng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>3.8181818E7</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>3818182.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>4.2E7</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>0401200101</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH VĨNH CHÂU</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Số 7 Lỗ Giáng 3, Phường Hòa Xuân, TP Đà Nẵng, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>4.8148148E7</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>3851852.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>5.2E7</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0312848204</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG TÂM ĐẮC E &amp; C</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Số 24 Đặng Thai Mai, Phường Cầu Kiệu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>596296.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>47704.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>644000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>0312848204</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG TÂM ĐẮC E &amp; C</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Số 24 Đặng Thai Mai, Phường Cầu Kiệu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>1400000.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>140000.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>1540000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/9/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/9/Hoadondientu.xlsx
@@ -314,6 +314,89 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25TTR</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0303765858</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG SONG HÂN</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>36/21 Đường D2, Phường Thạnh Mỹ Tây, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>9.6879175E7</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>7750334.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>1.04629509E8</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
